--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,6 +1264,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129178040</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1642</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Långskägg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Usnea longissima</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tvärhult, Tvärhult, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>415798</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6573642</v>
+      </c>
+      <c r="S7" t="n">
+        <v>80</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda Wall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda Wall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129178040</v>
       </c>
       <c r="B7" t="n">
-        <v>79233</v>
+        <v>79234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129178040</v>
       </c>
       <c r="B7" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,6 +1362,257 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129307779</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58095</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hammarö Tvärhult, Hammarön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>415744</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6573744</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129307929</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56915</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hammarö Tvärhult, Hammarön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>415855</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6573652</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129178040</v>
       </c>
       <c r="B7" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129307779</v>
       </c>
       <c r="B8" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>129307929</v>
       </c>
       <c r="B9" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,6 +1613,147 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129356657</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hammarö Tvärhult, Hammarön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>415794</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6573847</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129178040</v>
       </c>
       <c r="B7" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129178040</v>
       </c>
       <c r="B7" t="n">
-        <v>79242</v>
+        <v>79243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982623</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128982620</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128982617</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>129068789</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129068798</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -1270,7 +1270,7 @@
         <v>129178040</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129307779</v>
       </c>
       <c r="B8" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>129307929</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>129356657</v>
       </c>
       <c r="B10" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>129307779</v>
       </c>
       <c r="B8" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>129307929</v>
       </c>
       <c r="B9" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>129356657</v>
       </c>
       <c r="B10" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>129307779</v>
       </c>
       <c r="B8" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>129307929</v>
       </c>
       <c r="B9" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>129356657</v>
       </c>
       <c r="B10" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128982623</v>
+        <v>129178036</v>
       </c>
       <c r="B2" t="n">
-        <v>92870</v>
+        <v>79526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1642</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tvärhult, Tvärhult, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415844</v>
+        <v>415798</v>
       </c>
       <c r="R2" t="n">
-        <v>6573697</v>
+        <v>6573642</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:41</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:41</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Linda Wall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Linda Wall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128982620</v>
+        <v>128982617</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,13 +818,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415776</v>
+        <v>415772</v>
       </c>
       <c r="R3" t="n">
-        <v>6573712</v>
+        <v>6573705</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128982617</v>
+        <v>128982620</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415772</v>
+        <v>415776</v>
       </c>
       <c r="R4" t="n">
-        <v>6573705</v>
+        <v>6573712</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,60 +1008,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129068789</v>
+        <v>128982623</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillängen, Lillängen, Vrm</t>
+          <t>Tvärhult, Tvärhult, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415809</v>
+        <v>415844</v>
       </c>
       <c r="R5" t="n">
-        <v>6573727</v>
+        <v>6573697</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,60 +1126,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129068798</v>
+        <v>128982628</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillängen, Lillängen, Vrm</t>
+          <t>Tvärhult, Tvärhult, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415803</v>
+        <v>415921</v>
       </c>
       <c r="R6" t="n">
-        <v>6573743</v>
+        <v>6573670</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,22 +1202,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,48 +1244,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129178040</v>
+        <v>129068773</v>
       </c>
       <c r="B7" t="n">
-        <v>79269</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1642</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tvärhult, Tvärhult, Vrm</t>
+          <t>Lillängen, Lillängen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415798</v>
+        <v>415919</v>
       </c>
       <c r="R7" t="n">
-        <v>6573642</v>
+        <v>6573695</v>
       </c>
       <c r="S7" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,12 +1320,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Wall</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Wall</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129307779</v>
+        <v>129307929</v>
       </c>
       <c r="B8" t="n">
-        <v>58106</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,45 +1373,61 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hammarö Tvärhult, Hammarön, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>415744</v>
+        <v>415855</v>
       </c>
       <c r="R8" t="n">
-        <v>6573744</v>
+        <v>6573652</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129307929</v>
+        <v>129356657</v>
       </c>
       <c r="B9" t="n">
-        <v>56926</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>415855</v>
+        <v>415794</v>
       </c>
       <c r="R9" t="n">
-        <v>6573652</v>
+        <v>6573847</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,6 +1613,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1615,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129356657</v>
+        <v>129307779</v>
       </c>
       <c r="B10" t="n">
-        <v>56926</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,61 +1650,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hammarö Tvärhult, Hammarön, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>415794</v>
+        <v>415744</v>
       </c>
       <c r="R10" t="n">
-        <v>6573847</v>
+        <v>6573744</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1727,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,16 +1738,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1753,6 +1751,244 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129068789</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillängen, Lillängen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>415809</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6573727</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129068798</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillängen, Lillängen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>415803</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6573743</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47571-2025 artfynd.xlsx
+++ b/artfynd/A 47571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129178036</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982617</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982623</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982628</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068773</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,6 +1530,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129307929</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1636,6 +1676,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129356657</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1751,6 +1796,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129307779</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1870,6 +1920,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068789</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1989,8 +2044,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068798</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>